--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486762_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486762_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3994</v>
+        <v>7.7012</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8888</v>
+        <v>6.2402</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5106</v>
+        <v>1.4609</v>
       </c>
       <c r="G2" t="n">
         <v>6.3496</v>
@@ -610,13 +610,13 @@
         <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0498</v>
+        <v>1.3516</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9381</v>
+        <v>0.4133</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9879</v>
+        <v>0.9383</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2754</v>
+        <v>3.8422</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9705</v>
+        <v>5.4876</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6951</v>
+        <v>-1.6455</v>
       </c>
       <c r="G3" t="n">
         <v>-1.8935</v>
@@ -688,13 +688,13 @@
         <v>0.5792</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6676</v>
+        <v>1.2344</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0273</v>
+        <v>0.5444</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6403</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>5.8528</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9579</v>
+        <v>2.7718</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3995</v>
+        <v>2.0892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5584</v>
+        <v>0.6826</v>
       </c>
       <c r="G4" t="n">
         <v>0.8752</v>
@@ -766,13 +766,13 @@
         <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6619</v>
+        <v>0.4758</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.2688</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0828</v>
+        <v>0.2069</v>
       </c>
       <c r="V4" t="n">
         <v>1.2277</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0946</v>
+        <v>1.7203</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2263</v>
+        <v>0.266</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1317</v>
+        <v>1.4543</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3917</v>
+        <v>-2.0036</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.462</v>
+        <v>-1.8272</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8537</v>
+        <v>-0.1764</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>-1.4164</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9866</v>
+        <v>-1.6198</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8334</v>
+        <v>0.2035</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4283</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4486</v>
+        <v>-0.2074</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0203</v>
+        <v>-0.3799</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5098</v>
+        <v>1.5309</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3716</v>
+        <v>0.4547</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1381</v>
+        <v>1.0761</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2277</v>
+        <v>1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0596</v>
+        <v>1.0121</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3073</v>
+        <v>3.1438</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7522</v>
+        <v>-2.1317</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0036</v>
+        <v>1.3917</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8272</v>
+        <v>-0.462</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1764</v>
+        <v>1.8537</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4164</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.6198</v>
+        <v>0.9866</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2035</v>
+        <v>1.8334</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-1.4283</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2074</v>
+        <v>-1.4486</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3799</v>
+        <v>0.0203</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9654</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8701</v>
+        <v>1.4273</v>
       </c>
       <c r="T6" t="n">
-        <v>0.496</v>
+        <v>1.2892</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3741</v>
+        <v>0.1381</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2277</v>
+        <v>-1.2277</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5438</v>
+        <v>0.3881</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2091</v>
+        <v>1.954</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6653</v>
+        <v>-1.5659</v>
       </c>
       <c r="G7" t="n">
         <v>0.7536</v>
@@ -1000,13 +1000,13 @@
         <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1763</v>
+        <v>0.0206</v>
       </c>
       <c r="T7" t="n">
-        <v>0.248</v>
+        <v>-0.0071</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0717</v>
+        <v>0.0277</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2498</v>
+        <v>0.3686</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8249</v>
+        <v>0.5216</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.1529</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4796</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4671</v>
+        <v>1.5859</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1855</v>
+        <v>0.8822</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2815</v>
+        <v>0.7037</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5401</v>
+        <v>-1.9602</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0681</v>
+        <v>-0.5044</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6082</v>
+        <v>-1.4559</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3528</v>
+        <v>-4.243</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1103</v>
+        <v>-1.876</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2425</v>
+        <v>-2.3669</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.145</v>
+        <v>-1.8629</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2823</v>
+        <v>-0.5653</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8627</v>
+        <v>-1.2976</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2079</v>
+        <v>-2.3801</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.828</v>
+        <v>-1.3107</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3799</v>
+        <v>-1.0693</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3607</v>
+        <v>0.4758</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9854</v>
+        <v>0.1308</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3753</v>
+        <v>0.3449</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5133</v>
+        <v>1.2277</v>
       </c>
       <c r="W9" t="n">
         <v>1.2277</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6567</v>
+        <v>-2.1908</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0767</v>
+        <v>0.1442</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.58</v>
+        <v>-2.335</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.243</v>
+        <v>-3.3528</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.876</v>
+        <v>-1.1103</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3669</v>
+        <v>-2.2425</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8629</v>
+        <v>-2.145</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5653</v>
+        <v>-0.2823</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2976</v>
+        <v>-1.8627</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3801</v>
+        <v>-1.2079</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3107</v>
+        <v>-0.828</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0693</v>
+        <v>-0.3799</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2207</v>
+        <v>1.71</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4415</v>
+        <v>1.0615</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2208</v>
+        <v>0.6484</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2277</v>
+        <v>-1.5133</v>
       </c>
       <c r="W10" t="n">
         <v>1.2277</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6506</v>
+        <v>-2.9553</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2402</v>
+        <v>-2.8164</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4103</v>
+        <v>-0.1389</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1175</v>
+        <v>-2.4516</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0066</v>
+        <v>-0.3176</v>
       </c>
       <c r="I11" t="n">
+        <v>-2.134</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.8576</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-2.0232</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.594</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.4832</v>
+      </c>
+      <c r="O11" t="n">
         <v>-0.1108</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.3939</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.8138</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-2.5113</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-1.5867</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.9247</v>
-      </c>
       <c r="P11" t="n">
-        <v>-4.2477</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9423</v>
+        <v>0.724</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1928</v>
+        <v>0.0066</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7495</v>
+        <v>0.7174</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9938</v>
+        <v>-4.1308</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7059</v>
+        <v>-1.8266</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2879</v>
+        <v>-2.3043</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4516</v>
+        <v>-0.1175</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3176</v>
+        <v>-0.0066</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.134</v>
+        <v>-0.1108</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8576</v>
+        <v>2.3939</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1655</v>
+        <v>1.58</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0232</v>
+        <v>0.8138</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.594</v>
+        <v>-2.5113</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4832</v>
+        <v>-1.5867</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1108</v>
+        <v>-0.9247</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-4.2477</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9654</v>
+        <v>-4.827</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3145</v>
+        <v>1.462</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8829</v>
+        <v>0.6065</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5684</v>
+        <v>0.8555</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.739299999999997</v>
+        <v>6.567200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>13.8717</v>
+        <v>14.6992</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.132400000000001</v>
+        <v>-8.132299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.171500000000002</v>
+        <v>-6.1715</v>
       </c>
       <c r="H13" t="n">
         <v>-4.8262</v>
@@ -1447,7 +1447,7 @@
         <v>4.143800000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>5.177399999999998</v>
+        <v>5.177399999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-15.4928</v>
@@ -1456,7 +1456,7 @@
         <v>-8.9702</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.5227</v>
+        <v>-6.522699999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-4.8269</v>
@@ -1468,10 +1468,10 @@
         <v>7.7231</v>
       </c>
       <c r="S13" t="n">
-        <v>11.1704</v>
+        <v>11.9983</v>
       </c>
       <c r="T13" t="n">
-        <v>4.823200000000001</v>
+        <v>5.6509</v>
       </c>
       <c r="U13" t="n">
         <v>6.347</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0956</v>
+        <v>6.8143</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4018</v>
+        <v>6.1949</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6938</v>
+        <v>0.6193</v>
       </c>
       <c r="G14" t="n">
         <v>2.5832</v>
@@ -1546,13 +1546,13 @@
         <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0355</v>
+        <v>-2.3168</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8556</v>
+        <v>-1.0625</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1799</v>
+        <v>-1.2544</v>
       </c>
       <c r="V14" t="n">
         <v>5.1964</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9001</v>
+        <v>5.2258</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0271</v>
+        <v>4.3031</v>
       </c>
       <c r="F15" t="n">
-        <v>0.873</v>
+        <v>0.9227</v>
       </c>
       <c r="G15" t="n">
         <v>6.9151</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.015</v>
+        <v>-1.6893</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.111</v>
+        <v>-0.8349</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.904</v>
+        <v>-0.8544</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3495</v>
+        <v>-0.3733</v>
       </c>
       <c r="E16" t="n">
-        <v>2.778</v>
+        <v>0.5236</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1275</v>
+        <v>-0.8969</v>
       </c>
       <c r="G16" t="n">
-        <v>1.819</v>
+        <v>-0.7249</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4068</v>
+        <v>-0.2208</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5878</v>
+        <v>-0.5041</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4196</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3382</v>
+        <v>0.1242</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>0.572</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6006</v>
+        <v>-1.4211</v>
       </c>
       <c r="N16" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6692</v>
+        <v>-1.0761</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4854</v>
+        <v>0.1586</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3584</v>
+        <v>-0.1725</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8438</v>
+        <v>0.3311</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4767</v>
+        <v>-0.6231</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4202</v>
+        <v>-0.2907</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8969</v>
+        <v>-0.3324</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7249</v>
+        <v>1.6595</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2208</v>
+        <v>0.5179</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5041</v>
+        <v>1.1416</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6961000000000001</v>
+        <v>2.9232</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1242</v>
+        <v>1.4153</v>
       </c>
       <c r="L17" t="n">
-        <v>0.572</v>
+        <v>1.5079</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4211</v>
+        <v>-1.2637</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.345</v>
+        <v>-0.8973</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0761</v>
+        <v>-0.3663</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0552</v>
+        <v>-1.4757</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2759</v>
+        <v>-1.2831</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3311</v>
+        <v>-0.1926</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0286</v>
+        <v>-0.6846</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4975</v>
+        <v>2.4677</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5311</v>
+        <v>-3.1523</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6595</v>
+        <v>1.819</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5179</v>
+        <v>2.4068</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1416</v>
+        <v>-0.5878</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9232</v>
+        <v>2.4196</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4153</v>
+        <v>2.3382</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5079</v>
+        <v>0.0814</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2637</v>
+        <v>-0.6006</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8973</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3663</v>
+        <v>-0.6692</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8812</v>
+        <v>-0.8205</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4899</v>
+        <v>0.0481</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3913</v>
+        <v>-0.8686</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6138</v>
+        <v>-2.4554</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6138</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3886</v>
+        <v>-1.0576</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9161</v>
+        <v>1.1229</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3046</v>
+        <v>-2.1805</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6092</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.324</v>
+        <v>-0.993</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0485</v>
+        <v>-0.8416</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2755</v>
+        <v>-0.1513</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2506</v>
+        <v>-2.1182</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0765</v>
+        <v>-0.8696</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1741</v>
+        <v>-1.2486</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1734</v>
@@ -2092,13 +2092,13 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4634</v>
+        <v>-0.331</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1874</v>
+        <v>-0.2619</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7197</v>
+        <v>-3.4839</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2481</v>
+        <v>-3.9379</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5284</v>
+        <v>0.4539</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4219</v>
@@ -2170,13 +2170,13 @@
         <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0355</v>
+        <v>-1.7997</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5451</v>
+        <v>-1.2348</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4904</v>
+        <v>-0.5649</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5467</v>
+        <v>-7.464</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6762</v>
+        <v>-1.4694</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.8704</v>
+        <v>-5.9946</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1288</v>
@@ -2248,13 +2248,13 @@
         <v>1.9308</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7927</v>
+        <v>-1.71</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0485</v>
+        <v>-0.8416</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7442</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-4.6251</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.739400000000002</v>
+        <v>-5.739300000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>8.132499999999999</v>
+        <v>8.132200000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-13.8717</v>
@@ -2293,7 +2293,7 @@
         <v>6.171600000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.826299999999999</v>
+        <v>4.8263</v>
       </c>
       <c r="I24" t="n">
         <v>1.345299999999999</v>
@@ -2305,7 +2305,7 @@
         <v>8.9704</v>
       </c>
       <c r="L24" t="n">
-        <v>6.522800000000001</v>
+        <v>6.522799999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-9.321400000000001</v>
@@ -2314,7 +2314,7 @@
         <v>-4.144000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.177500000000001</v>
+        <v>-5.1775</v>
       </c>
       <c r="P24" t="n">
         <v>4.8269</v>
@@ -2326,13 +2326,13 @@
         <v>12.5501</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.1706</v>
+        <v>-11.1705</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.3472</v>
+        <v>-6.347199999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.8233</v>
+        <v>-4.823300000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-5.5671</v>
